--- a/2026_attendees_list.xlsx
+++ b/2026_attendees_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{35B32316-2A2A-48A1-8D9E-A84C4BEF1B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C85F9A42-9787-4BB3-B8DC-ADB56B3AA69A}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{35B32316-2A2A-48A1-8D9E-A84C4BEF1B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26867611-3826-4AE7-BDAA-76FD1BBB1D00}"/>
   <bookViews>
-    <workbookView xWindow="12530" yWindow="0" windowWidth="21770" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7720" yWindow="1990" windowWidth="21770" windowHeight="11300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="설문지 응답 시트1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="169">
   <si>
     <t>박현후</t>
   </si>
@@ -440,9 +440,6 @@
   </si>
   <si>
     <t>Yedarm Jung</t>
-  </si>
-  <si>
-    <t>카이스트</t>
   </si>
   <si>
     <t>이정훈</t>
@@ -1047,13 +1044,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1075,7 +1072,7 @@
         <v>56</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1086,18 +1083,18 @@
         <v>14</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="C5" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1182,10 +1179,10 @@
         <v>20</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1229,7 +1226,7 @@
         <v>136</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1240,18 +1237,18 @@
         <v>48</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="C19" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1259,7 +1256,7 @@
         <v>51</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>52</v>
@@ -1347,7 +1344,7 @@
         <v>18</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>19</v>
@@ -1361,7 +1358,7 @@
         <v>101</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1460,7 +1457,7 @@
         <v>107</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1468,7 +1465,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>25</v>
@@ -1504,7 +1501,7 @@
         <v>90</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1512,7 +1509,7 @@
         <v>11</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>12</v>
@@ -1603,7 +1600,7 @@
         <v>27</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1614,7 +1611,7 @@
         <v>77</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1625,18 +1622,18 @@
         <v>22</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1688,10 +1685,10 @@
         <v>124</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1702,7 +1699,7 @@
         <v>44</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1724,7 +1721,7 @@
         <v>4</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1734,8 +1731,8 @@
       <c r="B63" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>139</v>
+      <c r="C63" s="4" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1798,7 +1795,7 @@
         <v>108</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>2</v>
@@ -1806,10 +1803,10 @@
     </row>
     <row r="70" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>25</v>

--- a/2026_attendees_list.xlsx
+++ b/2026_attendees_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{35B32316-2A2A-48A1-8D9E-A84C4BEF1B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{372336EC-DDE3-477D-BEED-5D2178ADCE40}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{35B32316-2A2A-48A1-8D9E-A84C4BEF1B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{122C3CCF-A64D-400B-825F-D065CA1CD786}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5808" yWindow="612" windowWidth="16620" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="설문지 응답 시트1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="99">
   <si>
     <t>박현후</t>
   </si>
@@ -61,9 +61,6 @@
     <t>박재흥</t>
   </si>
   <si>
-    <t>천문연</t>
-  </si>
-  <si>
     <t>김선훈</t>
   </si>
   <si>
@@ -196,9 +193,6 @@
     <t>서행자</t>
   </si>
   <si>
-    <t>항공우주연구원</t>
-  </si>
-  <si>
     <t>박필재</t>
   </si>
   <si>
@@ -215,9 +209,6 @@
   </si>
   <si>
     <t>윤동석</t>
-  </si>
-  <si>
-    <t>우주과학과</t>
   </si>
   <si>
     <t>안범수</t>
@@ -427,6 +418,10 @@
   </si>
   <si>
     <t>한국과학기술원 기계기술연구소</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>경희대학교</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -822,254 +817,254 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:B73"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" customWidth="1"/>
-    <col min="3" max="8" width="18.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" customWidth="1"/>
+    <col min="3" max="8" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="21.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+    </row>
+    <row r="18" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+      <c r="B18" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
@@ -1077,103 +1072,103 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="B43" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>6</v>
       </c>
@@ -1181,127 +1176,127 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="B53" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>4</v>
       </c>
@@ -1309,23 +1304,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>9</v>
       </c>
@@ -1333,55 +1328,55 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="B69" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>3</v>
       </c>
@@ -1389,23 +1384,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>5</v>
       </c>

--- a/2026_attendees_list.xlsx
+++ b/2026_attendees_list.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beb95a8409ff7f4b/달탐사워크숍_2026/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{35B32316-2A2A-48A1-8D9E-A84C4BEF1B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{122C3CCF-A64D-400B-825F-D065CA1CD786}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="8_{35B32316-2A2A-48A1-8D9E-A84C4BEF1B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{753480B8-1FC9-4CA9-A5BD-6E25A5BCFA0B}"/>
   <bookViews>
-    <workbookView xWindow="5808" yWindow="612" windowWidth="16620" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="설문지 응답 시트1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'설문지 응답 시트1'!$A$1:$B$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'설문지 응답 시트1'!$A$1:$B$74</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="100">
   <si>
     <t>박현후</t>
   </si>
@@ -424,6 +424,10 @@
     <t>경희대학교</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>김기수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -440,6 +444,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -816,15 +821,15 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B73"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B74"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.88671875" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" customWidth="1"/>
-    <col min="3" max="8" width="18.88671875" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" customWidth="1"/>
+    <col min="3" max="8" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>93</v>
       </c>
@@ -832,7 +837,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>49</v>
       </c>
@@ -840,7 +845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>33</v>
       </c>
@@ -848,7 +853,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -856,7 +861,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>80</v>
       </c>
@@ -864,7 +869,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>52</v>
       </c>
@@ -872,7 +877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>58</v>
       </c>
@@ -880,7 +885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -888,523 +893,531 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="B11" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="B13" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B14" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+    <row r="15" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+    <row r="17" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+    <row r="18" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B18" s="4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+    <row r="19" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B19" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+    <row r="20" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B20" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+    <row r="21" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+    <row r="22" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+    <row r="23" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+    <row r="24" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="B24" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="B25" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="B26" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="B27" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+    <row r="29" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="B29" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B30" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+    <row r="31" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B31" s="4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+    <row r="32" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="B32" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="B33" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+    <row r="35" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B35" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+    <row r="36" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B36" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+    <row r="37" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="B37" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+    <row r="39" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+    <row r="40" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B40" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+    <row r="41" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+    <row r="42" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="B42" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="B43" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B44" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+    <row r="45" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+    <row r="46" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="B46" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="B47" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+      <c r="B48" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B49" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+    <row r="50" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="B50" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B51" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+    <row r="52" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B52" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
+    <row r="53" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B53" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+    <row r="54" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B54" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+    <row r="55" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B55" s="7" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+    <row r="56" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B56" s="5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+    <row r="57" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B57" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+    <row r="58" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
+    <row r="59" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B59" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+    <row r="60" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+      <c r="B60" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+      <c r="B61" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B62" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+    <row r="63" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B63" s="5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+    <row r="64" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+    <row r="65" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B65" s="5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+    <row r="66" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B66" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+    <row r="67" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+      <c r="B67" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+      <c r="B68" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B69" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+    <row r="70" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
+      <c r="B70" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+      <c r="B71" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+      <c r="B72" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B73" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
+    <row r="74" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B74" s="1" t="s">
         <v>1</v>
       </c>
     </row>
